--- a/benchmark/generated_files/CRED-2_M_013.xlsx
+++ b/benchmark/generated_files/CRED-2_M_013.xlsx
@@ -493,18 +493,18 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 62,17 EUR DEL 02.01.2026 A (ITA) IKEA BISTRO</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>83.81</v>
+        <v>62.17</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -514,18 +514,18 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46026</v>
+        <v>46028</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 30,64 EUR DEL 03.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 55,56 EUR DEL 04.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>30.64</v>
+        <v>55.56</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -538,15 +538,15 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 106,43 EUR DEL 04.01.2026 A (ITA) FARMACIA COMUNALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 67,51 EUR DEL 04.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>106.43</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 198,57 EUR DEL 04.01.2026 A (ITA) OTTICA AVANZI</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6.01</v>
+        <v>198.57</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -580,11 +580,11 @@
         <v>46026</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 98,29 EUR DEL 04.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 98,29 EUR DEL 04.01.2026 A (ITA) MAXI ZOO</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -601,11 +601,11 @@
         <v>46027</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 24,32 EUR DEL 05.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 24,32 EUR DEL 05.01.2026 A (ITA) O'TACOS</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -626,11 +626,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 18,44 EUR DEL 05.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2198 SUPERMERCATI ZAZZERON LIVORNO</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>18.44</v>
+        <v>72.53</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -640,18 +640,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 36,98 EUR DEL 05.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6273 LAFARMACIA. NORD</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.98</v>
+        <v>133.35</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -661,18 +661,18 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 139,67 EUR DEL 05.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 100,17 EUR DEL 06.01.2026 A (ITA) PRIMADONNA OVEST</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>139.67</v>
+        <v>100.17</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -682,18 +682,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 72,53 EUR DEL 05.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 25,41 EUR DEL 06.01.2026 A (ITA) KEBHOUZE FUORIGROTTA</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>72.53</v>
+        <v>25.41</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -703,18 +703,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 14,32 EUR DEL 07.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 197,63 EUR DEL 06.01.2026 A (ITA) RAY-BAN NORD</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14.32</v>
+        <v>197.63</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -724,18 +724,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 224,67 EUR DEL 07.01.2026 A (ITA) FARMACIA DR ROSSI</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>80.68000000000001</v>
+        <v>224.67</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -745,18 +745,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 60,69 EUR DEL 08.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9682 UBIK CENTRO COMMERCIALE LE GRANGE</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>60.69</v>
+        <v>204.36</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -766,18 +766,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,70 EUR DEL 10.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,39 EUR DEL 07.01.2026 A (ITA) FLOWER BURGER ASSAGO</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>69.7</v>
+        <v>35.39</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -787,18 +787,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 77,40 EUR DEL 10.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8370 SIGMA CAGLIARI</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -808,18 +808,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 29,77 EUR DEL 07.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>562.24</v>
+        <v>29.77</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -829,18 +829,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46034</v>
+        <v>46029</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 8,08 EUR DEL 11.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 54,75 EUR DEL 07.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8.08</v>
+        <v>54.75</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46036</v>
+        <v>46030</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,57 EUR DEL 12.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 157,78 EUR DEL 08.01.2026 A (ITA) PRIX FUORIGROTTA</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15.57</v>
+        <v>157.78</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -871,18 +871,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46035</v>
+        <v>46031</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 6579 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2814 LAFARMACIA.</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>140.03</v>
+        <v>241.58</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -892,18 +892,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46035</v>
+        <v>46031</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>Pagam. POS - PAGAMENTO POS 126,79 EUR DEL 09.01.2026 A (ITA) HOKA</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>56.63</v>
+        <v>126.79</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -913,18 +913,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46035</v>
+        <v>46031</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 90,69 EUR DEL 13.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,36 EUR DEL 09.01.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>90.69</v>
+        <v>81.36</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -934,18 +934,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 49,47 EUR DEL 13.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 65,56 EUR DEL 11.01.2026 A (ITA) ACQUA &amp; SAPONE</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>49.47</v>
+        <v>65.56</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -955,18 +955,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>46035</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 42,13 EUR DEL 13.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 138,30 EUR DEL 11.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>42.13</v>
+        <v>138.3</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -976,18 +976,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 87,80 EUR DEL 13.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>87.8</v>
+        <v>14.41</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -997,18 +997,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46039</v>
+        <v>46035</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 123,91 EUR DEL 15.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 17,60 EUR DEL 13.01.2026 A (ITA) PRIMOR PALERMO</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>123.91</v>
+        <v>17.6</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1018,18 +1018,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 168,28 EUR DEL 15.01.2026 A (ITA) OTTICA AVANZI</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>168.28</v>
+        <v>5.72</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1039,18 +1039,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46040</v>
+        <v>46037</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 75,02 EUR DEL 15.01.2026 A (ITA) PETMARK</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>36.5</v>
+        <v>75.02</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1060,18 +1060,18 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46042</v>
+        <v>46037</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:215269952 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>52.63</v>
+        <v>11.37</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1081,18 +1081,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 202,47 EUR DEL 19.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4951 GULLIVER</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>202.47</v>
+        <v>113.23</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1102,18 +1102,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46041</v>
+        <v>46038</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,91 EUR DEL 16.01.2026 A (ITA) CADDY'S CENTRO COMM. IL LEONE</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>6.7</v>
+        <v>35.91</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1123,18 +1123,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>46042</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 84,59 EUR DEL 19.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 216,60 EUR DEL 18.01.2026 A (ITA) GRANDVISION</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>84.59</v>
+        <v>216.6</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1144,18 +1144,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 156,61 EUR DEL 21.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 48,29 EUR DEL 18.01.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>156.61</v>
+        <v>48.29</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1165,18 +1165,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,87 EUR DEL 21.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1396 CONAD</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>12.87</v>
+        <v>178.75</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1186,18 +1186,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46044</v>
+        <v>46040</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,02 EUR DEL 22.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 65,03 EUR DEL 18.01.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>32.02</v>
+        <v>65.03</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1207,18 +1207,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 63,76 EUR DEL 22.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-217292886</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1228,18 +1228,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 100,72 EUR DEL 22.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,71 EUR DEL 21.01.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>100.72</v>
+        <v>10.71</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1249,18 +1249,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 295,93 EUR DEL 21.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.51</v>
+        <v>295.93</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1270,18 +1270,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,51 EUR DEL 22.01.2026 A (ITA) ROSSOPOMODORO</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>21.51</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1291,18 +1291,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 40,41 EUR DEL 23.01.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>40.41</v>
+        <v>609.76</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 534,14 EUR DEL 24.01.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 119,30 EUR DEL 25.01.2026 A (ITA) GABOR</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>534.14</v>
+        <v>119.3</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1333,18 +1333,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 134,41 EUR DEL 26.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1278 MIGROS</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>134.41</v>
+        <v>111.56</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1354,18 +1354,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,33 EUR DEL 26.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 155,03 EUR DEL 27.01.2026 A (ITA) CONAD CITY ROMA</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>15.33</v>
+        <v>155.03</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1378,15 +1378,15 @@
         <v>46049</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 155,03 EUR DEL 27.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 30,12 EUR DEL 27.01.2026 A (ITA) SPORTLER</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>155.03</v>
+        <v>30.12</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 6,94 EUR DEL 27.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8113 ALE-HOP</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>6.94</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1424,11 +1424,11 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 89,29 EUR DEL 27.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Pagam. POS - PAGAMENTO POS 141,07 EUR DEL 27.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>89.29000000000001</v>
+        <v>141.07</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1438,18 +1438,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6699 DM</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>11.7</v>
+        <v>118.82</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1462,15 +1462,15 @@
         <v>46050</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,67 EUR DEL 28.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>62.67</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1480,18 +1480,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 56,62 EUR DEL 29.01.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>56.62</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -1501,18 +1501,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210104984</t>
+          <t>Pagam. POS - PAGAMENTO POS 160,29 EUR DEL 29.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>14.84</v>
+        <v>160.29</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -1543,18 +1543,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 29,52 EUR DEL 30.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 61,30 EUR DEL 31.01.2026 A (ITA) PITTAROSSO</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>29.52</v>
+        <v>61.3</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -1564,18 +1564,18 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:216971116 BEN. DR VERDI ODONTOIATRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 147,10 EUR DEL 31.01.2026 A (ITA) IKEA SWEDISH FOOD MARKET</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>71.86</v>
+        <v>147.1</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 55,11 EUR DEL 01.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 23,21 EUR DEL 01.02.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>55.11</v>
+        <v>23.21</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -1606,18 +1606,18 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,69 EUR DEL 02.02.2026 A (ITA) COOP LOMBARDIA</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>27.42</v>
+        <v>59.69</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -1634,11 +1634,11 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 58,83 EUR DEL 03.02.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 58,35 EUR DEL 03.02.2026 A (ITA) SIGMA PORTA NUOVA</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>58.83</v>
+        <v>58.35</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,09 EUR DEL 03.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 106,84 EUR DEL 03.02.2026 A (ITA) PRIMADONNA</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>15.09</v>
+        <v>106.84</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -1672,15 +1672,15 @@
         <v>46056</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:216747689 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Disposizione - RIF:219528637 BEN. DR VERDI ODONTOIATRA</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>57.99</v>
+        <v>8.82</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -1690,18 +1690,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 54,45 EUR DEL 04.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 137,88 EUR DEL 03.02.2026 A (ITA) PITTAROSSO</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>54.45</v>
+        <v>137.88</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -1711,18 +1711,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2986 TRATTORIA LA PERGOLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 31,78 EUR DEL 03.02.2026 A (ITA) JOHNSON FITNESS &amp; WELLNESS</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>83.11</v>
+        <v>31.78</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -1732,18 +1732,18 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 31,86 EUR DEL 06.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5066 MD</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>31.86</v>
+        <v>58.83</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -1753,18 +1753,18 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46061</v>
+        <v>46057</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9339 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 84,68 EUR DEL 04.02.2026 A (ITA) BREWDOG PALERMO</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>144.96</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 21,64 EUR DEL 07.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 15,67 EUR DEL 05.02.2026 A (ITA) HOKA</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>21.64</v>
+        <v>15.67</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1795,18 +1795,18 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B65" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>10.44</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -1816,18 +1816,18 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46060</v>
+        <v>46059</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46062</v>
+        <v>46059</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 6625 ESSELUNGA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3691 ITALMARK</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>46.12</v>
+        <v>55.76</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -1837,18 +1837,18 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5024 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7054 DM MODENA</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>16.4</v>
+        <v>31.6</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -1858,18 +1858,18 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B68" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>46063</v>
-      </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 8,69 EUR DEL 07.02.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>14.42</v>
+        <v>8.69</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -1879,18 +1879,18 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46062</v>
+        <v>46060</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46064</v>
+        <v>46061</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9957 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 720,70 EUR DEL 07.02.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>112.74</v>
+        <v>720.7</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1627 OVS S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1328 MALVÓN BERGAMO</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>59.8</v>
+        <v>71.94</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -1921,18 +1921,18 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 321,06 EUR DEL 10.02.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>321.06</v>
+        <v>14.42</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -1942,18 +1942,18 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>58.56</v>
+        <v>10.71</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -1963,18 +1963,18 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4997 LIDL ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7807 SCARPE&amp;SCARPE</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>121.96</v>
+        <v>109.88</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -1984,18 +1984,18 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 152,60 EUR DEL 12.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>152.6</v>
+        <v>7.02</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2005,18 +2005,18 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 9,85 EUR DEL 11.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>14.72</v>
+        <v>9.85</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2026,18 +2026,18 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46066</v>
+        <v>46064</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 40,24 EUR DEL 13.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Disposizione - RIF:218651395 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>40.24</v>
+        <v>154.29</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2047,18 +2047,18 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B77" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 165,55 EUR DEL 13.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5875 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>165.55</v>
+        <v>58.56</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2068,18 +2068,18 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 161,75 EUR DEL 13.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 78,02 EUR DEL 12.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>161.75</v>
+        <v>78.02</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2089,18 +2089,18 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46070</v>
+        <v>46065</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 72,64 EUR DEL 15.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,74 EUR DEL 12.02.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>72.64</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2110,18 +2110,18 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1420 LIDL ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9523 ESSELUNGA S.P.A.</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>75.29000000000001</v>
+        <v>121.96</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -2131,18 +2131,18 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>46068</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 31,69 EUR DEL 15.02.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 25,30 EUR DEL 13.02.2026 A (ITA) STROILI ORO NAPOLI</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>31.69</v>
+        <v>25.3</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -2152,18 +2152,18 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5581 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 55,69 EUR DEL 13.02.2026 A (ITA) THUN PRATI</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>66.12</v>
+        <v>55.69</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -2173,18 +2173,18 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 49,92 EUR DEL 16.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 6,27 EUR DEL 14.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>49.92</v>
+        <v>6.27</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -2194,18 +2194,18 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 97,31 EUR DEL 17.02.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 61,65 EUR DEL 16.02.2026 A (ITA) STARBUCKS RESERVE VIMODRONE</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>97.31</v>
+        <v>61.65</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -2215,18 +2215,18 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46071</v>
+        <v>46069</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 63,43 EUR DEL 18.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>63.43</v>
+        <v>12.63</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -2236,18 +2236,18 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46071</v>
+        <v>46069</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46071</v>
+        <v>46069</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-213100912</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>41.78</v>
+        <v>13.63</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -2260,15 +2260,15 @@
         <v>46071</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 126,04 EUR DEL 18.02.2026 A (ITA) CENTRO MEDICO SANTAGOSTINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3606 ACQUA &amp; SAPONE BOLOGNA</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>126.04</v>
+        <v>133.82</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -2278,18 +2278,18 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9847 DENTALPRO</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>5.26</v>
+        <v>78.7</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -2299,18 +2299,18 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210140625 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6486 MAXI ZOO</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>57.49</v>
+        <v>41.78</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -2323,15 +2323,15 @@
         <v>46072</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 79,38 EUR DEL 19.02.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 186,60 EUR DEL 19.02.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>79.38</v>
+        <v>186.6</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -2344,15 +2344,15 @@
         <v>46072</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 19,18 EUR DEL 19.02.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3690 DOPPIO MALTO</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>19.18</v>
+        <v>29.86</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -2365,15 +2365,15 @@
         <v>46074</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-218828362</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.88</v>
+        <v>6.01</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -2386,15 +2386,15 @@
         <v>46074</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3402 SIGMA</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>10.28</v>
+        <v>154.02</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -2404,18 +2404,18 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 65,09 EUR DEL 21.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>65.09</v>
+        <v>6.34</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -2428,15 +2428,15 @@
         <v>46075</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1868 CADDY'S TORINO</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>6.34</v>
+        <v>37.98</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -2446,18 +2446,18 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46075</v>
+        <v>46078</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 33,45 EUR DEL 22.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 14,24 EUR DEL 24.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>33.45</v>
+        <v>14.24</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -2467,18 +2467,18 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 47,43 EUR DEL 22.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 43,82 EUR DEL 24.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>47.43</v>
+        <v>43.82</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -2488,18 +2488,18 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46075</v>
+        <v>46078</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4042 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 104,89 EUR DEL 25.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>148.22</v>
+        <v>104.89</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -2509,18 +2509,18 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,65 EUR DEL 23.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 138,04 EUR DEL 25.02.2026 A (ITA) GABOR PERUGIA</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>13.65</v>
+        <v>138.04</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -2530,18 +2530,18 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 10,27 EUR DEL 24.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4487 TIGRE CORSICO</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>10.27</v>
+        <v>139.19</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -2551,18 +2551,18 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 81,05 EUR DEL 24.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 38,17 EUR DEL 26.02.2026 A (ITA) VITALDENT GENOVA</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>81.05</v>
+        <v>38.17</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -2572,18 +2572,18 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5612 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 67,44 EUR DEL 26.02.2026 A (ITA) NAU! VOMERO</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>81.86</v>
+        <v>67.44</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 82,96 EUR DEL 27.02.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2701 NATURA MARGHERA</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>82.95999999999999</v>
+        <v>80.44</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -2617,15 +2617,15 @@
         <v>46081</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46083</v>
+        <v>46081</v>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,28 EUR DEL 28.02.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 44,18 EUR DEL 28.02.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>57.28</v>
+        <v>44.18</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Saldo finale: 17.796,77 EUR</t>
+          <t>Saldo finale: 6.545,05 EUR</t>
         </is>
       </c>
     </row>
